--- a/Res_ConvLSTM/DroughtDataset_model_testing_1753806888_h_3.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1753806888_h_3.xlsx
@@ -658,7 +658,7 @@
         <v>0.008417747105701008</v>
       </c>
       <c r="C2" t="n">
-        <v>18938934</v>
+        <v>6312978</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>18938934</v>
+        <v>6312978</v>
       </c>
       <c r="K2" t="n">
-        <v>14413143</v>
+        <v>4648576</v>
       </c>
       <c r="L2" t="n">
-        <v>8676893</v>
+        <v>2675604</v>
       </c>
       <c r="M2" t="n">
-        <v>2185890</v>
+        <v>653583</v>
       </c>
       <c r="N2" t="n">
-        <v>77375</v>
+        <v>18487</v>
       </c>
       <c r="O2" t="n">
-        <v>1275191</v>
+        <v>389402</v>
       </c>
       <c r="P2" t="n">
-        <v>437478</v>
+        <v>134613</v>
       </c>
       <c r="Q2" t="n">
         <v>0.9999390244483948</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9362888336181641</v>
+        <v>0.9017469882965088</v>
       </c>
       <c r="S2" t="n">
-        <v>0.877505362033844</v>
+        <v>0.8162246346473694</v>
       </c>
       <c r="T2" t="n">
-        <v>0.848081111907959</v>
+        <v>0.7570032477378845</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3385977447032928</v>
+        <v>0.2540749311447144</v>
       </c>
       <c r="V2" t="n">
-        <v>0.8499635457992554</v>
+        <v>0.7822113037109375</v>
       </c>
       <c r="W2" t="n">
-        <v>0.9501963257789612</v>
+        <v>0.90241938829422</v>
       </c>
       <c r="X2" t="n">
-        <v>18938934</v>
+        <v>6312978</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>18938934</v>
+        <v>6312978</v>
       </c>
       <c r="AF2" t="n">
-        <v>14462079</v>
+        <v>4815402</v>
       </c>
       <c r="AG2" t="n">
-        <v>8899088</v>
+        <v>2970254</v>
       </c>
       <c r="AH2" t="n">
-        <v>2397713</v>
+        <v>799435</v>
       </c>
       <c r="AI2" t="n">
-        <v>176916</v>
+        <v>58995</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1376789</v>
+        <v>459097</v>
       </c>
       <c r="AK2" t="n">
-        <v>540046</v>
+        <v>180028</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9566799402236938</v>
+        <v>0.9565494656562805</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9112439155578613</v>
+        <v>0.9113017320632935</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8581776022911072</v>
+        <v>0.8579359650611877</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6626315712928772</v>
+        <v>0.6623888611793518</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9020464420318604</v>
+        <v>0.9020065665245056</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314221143722534</v>
+        <v>0.9314266443252563</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.002018670822238358</v>
       </c>
       <c r="C3" t="n">
-        <v>1086</v>
+        <v>362</v>
       </c>
       <c r="D3" t="n">
-        <v>14413143</v>
+        <v>4648576</v>
       </c>
       <c r="E3" t="n">
-        <v>681783</v>
+        <v>376520</v>
       </c>
       <c r="F3" t="n">
-        <v>4928</v>
+        <v>2808</v>
       </c>
       <c r="G3" t="n">
-        <v>648</v>
+        <v>329</v>
       </c>
       <c r="H3" t="n">
-        <v>146</v>
+        <v>105</v>
       </c>
       <c r="I3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J3" t="n">
-        <v>30048711</v>
+        <v>10016237</v>
       </c>
       <c r="K3" t="n">
-        <v>32906298</v>
+        <v>10794396</v>
       </c>
       <c r="L3" t="n">
-        <v>37998694</v>
+        <v>12462988</v>
       </c>
       <c r="M3" t="n">
-        <v>45801950</v>
+        <v>15187681</v>
       </c>
       <c r="N3" t="n">
-        <v>48570461</v>
+        <v>16186196</v>
       </c>
       <c r="O3" t="n">
-        <v>47236766</v>
+        <v>15712002</v>
       </c>
       <c r="P3" t="n">
-        <v>48386024</v>
+        <v>16121743</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9544029235839844</v>
+        <v>0.9244087338447571</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8873111009597778</v>
+        <v>0.8196833729743958</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7819915413856506</v>
+        <v>0.701179027557373</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2895792722702026</v>
+        <v>0.2074184566736221</v>
       </c>
       <c r="V3" t="n">
-        <v>0.8351306319236755</v>
+        <v>0.7647659778594971</v>
       </c>
       <c r="W3" t="n">
-        <v>0.7544727325439453</v>
+        <v>0.6963906288146973</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>14462079</v>
+        <v>4815402</v>
       </c>
       <c r="Z3" t="n">
-        <v>593526</v>
+        <v>197896</v>
       </c>
       <c r="AA3" t="n">
-        <v>25572</v>
+        <v>8540</v>
       </c>
       <c r="AB3" t="n">
-        <v>20336</v>
+        <v>6789</v>
       </c>
       <c r="AC3" t="n">
-        <v>135</v>
+        <v>45</v>
       </c>
       <c r="AD3" t="n">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>30049866</v>
+        <v>10016622</v>
       </c>
       <c r="AF3" t="n">
-        <v>33232195</v>
+        <v>11082162</v>
       </c>
       <c r="AG3" t="n">
-        <v>38343158</v>
+        <v>12776309</v>
       </c>
       <c r="AH3" t="n">
-        <v>45797268</v>
+        <v>15265103</v>
       </c>
       <c r="AI3" t="n">
-        <v>48631528</v>
+        <v>16210402</v>
       </c>
       <c r="AJ3" t="n">
-        <v>47312358</v>
+        <v>15770546</v>
       </c>
       <c r="AK3" t="n">
-        <v>48369192</v>
+        <v>16123045</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9576433300971985</v>
+        <v>0.957583487033844</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.910033106803894</v>
+        <v>0.9099507331848145</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8577702045440674</v>
+        <v>0.8576524257659912</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.662115752696991</v>
+        <v>0.6619057655334473</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9016677737236023</v>
+        <v>0.9016434550285339</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9313610792160034</v>
+        <v>0.9313350915908813</v>
       </c>
     </row>
     <row r="4">
@@ -929,127 +929,127 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>908084</v>
+        <v>474318</v>
       </c>
       <c r="E4" t="n">
-        <v>8676893</v>
+        <v>2675604</v>
       </c>
       <c r="F4" t="n">
-        <v>186302</v>
+        <v>108051</v>
       </c>
       <c r="G4" t="n">
-        <v>2903</v>
+        <v>2228</v>
       </c>
       <c r="H4" t="n">
-        <v>4461</v>
+        <v>3798</v>
       </c>
       <c r="I4" t="n">
-        <v>219</v>
+        <v>193</v>
       </c>
       <c r="J4" t="n">
-        <v>1155</v>
+        <v>385</v>
       </c>
       <c r="K4" t="n">
-        <v>980764</v>
+        <v>506502</v>
       </c>
       <c r="L4" t="n">
-        <v>1211244</v>
+        <v>602420</v>
       </c>
       <c r="M4" t="n">
-        <v>391564</v>
+        <v>209799</v>
       </c>
       <c r="N4" t="n">
-        <v>151141</v>
+        <v>54275</v>
       </c>
       <c r="O4" t="n">
-        <v>225098</v>
+        <v>108420</v>
       </c>
       <c r="P4" t="n">
-        <v>22930</v>
+        <v>14556</v>
       </c>
       <c r="Q4" t="n">
         <v>0.9999695420265198</v>
       </c>
       <c r="R4" t="n">
-        <v>0.945259153842926</v>
+        <v>0.9129372835159302</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8823809623718262</v>
+        <v>0.8179503083229065</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8136966228485107</v>
+        <v>0.7280225157737732</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3121759593486786</v>
+        <v>0.228388249874115</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8424818515777588</v>
+        <v>0.7733902931213379</v>
       </c>
       <c r="W4" t="n">
-        <v>0.841098427772522</v>
+        <v>0.7861301898956299</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>611398</v>
+        <v>204218</v>
       </c>
       <c r="Z4" t="n">
-        <v>8899088</v>
+        <v>2970254</v>
       </c>
       <c r="AA4" t="n">
-        <v>248302</v>
+        <v>83015</v>
       </c>
       <c r="AB4" t="n">
-        <v>16438</v>
+        <v>5489</v>
       </c>
       <c r="AC4" t="n">
-        <v>3432</v>
+        <v>1148</v>
       </c>
       <c r="AD4" t="n">
-        <v>204</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>654867</v>
+        <v>218736</v>
       </c>
       <c r="AG4" t="n">
-        <v>866780</v>
+        <v>289099</v>
       </c>
       <c r="AH4" t="n">
-        <v>396246</v>
+        <v>132377</v>
       </c>
       <c r="AI4" t="n">
-        <v>90074</v>
+        <v>30069</v>
       </c>
       <c r="AJ4" t="n">
-        <v>149506</v>
+        <v>49876</v>
       </c>
       <c r="AK4" t="n">
-        <v>39762</v>
+        <v>13254</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9571613669395447</v>
+        <v>0.9570662379264832</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9106380939483643</v>
+        <v>0.910625696182251</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8579738140106201</v>
+        <v>0.8577942252159119</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6623735427856445</v>
+        <v>0.6621472835540771</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9018570184707642</v>
+        <v>0.9018250107765198</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313915967941284</v>
+        <v>0.9313808679580688</v>
       </c>
     </row>
     <row r="5">
@@ -1059,152 +1059,152 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>45952</v>
+        <v>19631</v>
       </c>
       <c r="E5" t="n">
-        <v>464441</v>
+        <v>202694</v>
       </c>
       <c r="F5" t="n">
-        <v>2185890</v>
+        <v>653583</v>
       </c>
       <c r="G5" t="n">
-        <v>35790</v>
+        <v>14877</v>
       </c>
       <c r="H5" t="n">
-        <v>61436</v>
+        <v>39933</v>
       </c>
       <c r="I5" t="n">
-        <v>1777</v>
+        <v>1402</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>688595</v>
+        <v>380126</v>
       </c>
       <c r="L5" t="n">
-        <v>1101969</v>
+        <v>588588</v>
       </c>
       <c r="M5" t="n">
-        <v>609396</v>
+        <v>278537</v>
       </c>
       <c r="N5" t="n">
-        <v>189823</v>
+        <v>70642</v>
       </c>
       <c r="O5" t="n">
-        <v>251745</v>
+        <v>119776</v>
       </c>
       <c r="P5" t="n">
-        <v>142368</v>
+        <v>58688</v>
       </c>
       <c r="Q5" t="n">
         <v>0.9999763965606689</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9659236669540405</v>
+        <v>0.9457042217254639</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9527807831764221</v>
+        <v>0.9270644783973694</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9795675873756409</v>
+        <v>0.9700950384140015</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9930399656295776</v>
+        <v>0.9923502802848816</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9902662634849548</v>
+        <v>0.9860256314277649</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9966257810592651</v>
+        <v>0.9955146312713623</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>23984</v>
+        <v>8010</v>
       </c>
       <c r="Z5" t="n">
-        <v>254565</v>
+        <v>84966</v>
       </c>
       <c r="AA5" t="n">
-        <v>2397713</v>
+        <v>799435</v>
       </c>
       <c r="AB5" t="n">
-        <v>29795</v>
+        <v>9941</v>
       </c>
       <c r="AC5" t="n">
-        <v>87330</v>
+        <v>29135</v>
       </c>
       <c r="AD5" t="n">
-        <v>1899</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>639659</v>
+        <v>213300</v>
       </c>
       <c r="AG5" t="n">
-        <v>879774</v>
+        <v>293938</v>
       </c>
       <c r="AH5" t="n">
-        <v>397573</v>
+        <v>132685</v>
       </c>
       <c r="AI5" t="n">
-        <v>90282</v>
+        <v>30134</v>
       </c>
       <c r="AJ5" t="n">
-        <v>150147</v>
+        <v>50081</v>
       </c>
       <c r="AK5" t="n">
-        <v>39800</v>
+        <v>13273</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9735750555992126</v>
+        <v>0.9735427498817444</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9643478989601135</v>
+        <v>0.9642956852912903</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9837958812713623</v>
+        <v>0.9837679862976074</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963183999061584</v>
+        <v>0.9963132739067078</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9938832521438599</v>
+        <v>0.9938787817955017</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983758926391602</v>
+        <v>0.9983755350112915</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>60</v>
+        <v>22</v>
       </c>
       <c r="D6" t="n">
-        <v>26523</v>
+        <v>12460</v>
       </c>
       <c r="E6" t="n">
-        <v>58066</v>
+        <v>17359</v>
       </c>
       <c r="F6" t="n">
-        <v>83281</v>
+        <v>31833</v>
       </c>
       <c r="G6" t="n">
-        <v>77375</v>
+        <v>18487</v>
       </c>
       <c r="H6" t="n">
-        <v>21481</v>
+        <v>8685</v>
       </c>
       <c r="I6" t="n">
-        <v>412</v>
+        <v>283</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>19318</v>
+        <v>6452</v>
       </c>
       <c r="Z6" t="n">
-        <v>16016</v>
+        <v>5347</v>
       </c>
       <c r="AA6" t="n">
-        <v>32584</v>
+        <v>10875</v>
       </c>
       <c r="AB6" t="n">
-        <v>176916</v>
+        <v>58995</v>
       </c>
       <c r="AC6" t="n">
-        <v>20921</v>
+        <v>6979</v>
       </c>
       <c r="AD6" t="n">
-        <v>1443</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1263,22 +1263,22 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>103</v>
+        <v>49</v>
       </c>
       <c r="E7" t="n">
-        <v>6587</v>
+        <v>5594</v>
       </c>
       <c r="F7" t="n">
-        <v>115080</v>
+        <v>65689</v>
       </c>
       <c r="G7" t="n">
-        <v>109457</v>
+        <v>35768</v>
       </c>
       <c r="H7" t="n">
-        <v>1275191</v>
+        <v>389402</v>
       </c>
       <c r="I7" t="n">
-        <v>20518</v>
+        <v>12676</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>83</v>
+        <v>28</v>
       </c>
       <c r="Z7" t="n">
-        <v>2430</v>
+        <v>809</v>
       </c>
       <c r="AA7" t="n">
-        <v>88798</v>
+        <v>29617</v>
       </c>
       <c r="AB7" t="n">
-        <v>22710</v>
+        <v>7585</v>
       </c>
       <c r="AC7" t="n">
-        <v>1376789</v>
+        <v>459097</v>
       </c>
       <c r="AD7" t="n">
-        <v>36126</v>
+        <v>12042</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>102</v>
+        <v>44</v>
       </c>
       <c r="E8" t="n">
-        <v>367</v>
+        <v>253</v>
       </c>
       <c r="F8" t="n">
-        <v>1973</v>
+        <v>1418</v>
       </c>
       <c r="G8" t="n">
-        <v>2343</v>
+        <v>1073</v>
       </c>
       <c r="H8" t="n">
-        <v>137574</v>
+        <v>55899</v>
       </c>
       <c r="I8" t="n">
-        <v>437478</v>
+        <v>134613</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>84</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>243</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>990</v>
+        <v>330</v>
       </c>
       <c r="AB8" t="n">
-        <v>795</v>
+        <v>265</v>
       </c>
       <c r="AC8" t="n">
-        <v>37688</v>
+        <v>12569</v>
       </c>
       <c r="AD8" t="n">
-        <v>540046</v>
+        <v>180028</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
